--- a/output/pdf_financials_xlsx/PVT.xlsx
+++ b/output/pdf_financials_xlsx/PVT.xlsx
@@ -1916,16 +1916,16 @@
         <v>56.064467</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>27.156661</v>
+        <v>2.586374</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>20.039797</v>
+        <v>2.546891</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12.190163</v>
+        <v>2.223202</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.229014</v>
+        <v>1.351327</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/output/pdf_financials_xlsx/PVT.xlsx
+++ b/output/pdf_financials_xlsx/PVT.xlsx
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.602302</v>
+        <v>39.403556</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.91932</v>
+        <v>41.811038</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4.202619</v>
+        <v>56.092447</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.394136</v>
+        <v>48.325102</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.011714</v>
+        <v>44.976542</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>32.850877</v>
+        <v>-5.950377</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>27.956147</v>
+        <v>-11.935571</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>41.526359</v>
+        <v>-10.363469</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>39.090253</v>
+        <v>-6.840713</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>31.79098</v>
+        <v>-11.173848</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -769,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.208638</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.064694</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.223032</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.151409</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -1269,16 +1269,16 @@
         <v>-5.758277</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.726933</v>
+        <v>-11.935571</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-10.298775</v>
+        <v>-10.363469</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.617681</v>
+        <v>-6.840713</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-11.022439</v>
+        <v>-11.173848</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1333,16 +1333,16 @@
         <v>-1.440009</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.233082</v>
+        <v>-6.44172</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.677538</v>
+        <v>-1.742232</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.206174</v>
+        <v>-0.429206</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.878743</v>
+        <v>-4.030152</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         <v>-2.264316867654195</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-9.228139845119413</v>
+        <v>-9.537030477555506</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1.649602347163306</v>
+        <v>-1.71321901292431</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2295775817704082</v>
+        <v>-0.4779267781648017</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-4.957340086464347</v>
+        <v>-5.150852754138251</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -1465,19 +1465,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>53.942263</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>24.570287</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>17.346028</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>7.290149</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.877687</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -1529,19 +1529,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>53.942263</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>24.570287</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>17.346028</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>7.290149</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.877687</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>56.064467</v>
+        <v>2.122204</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>2.586374</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.546891</v>
+        <v>2.693769</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.223202</v>
+        <v>4.900014</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>1.351327</v>
@@ -4333,16 +4333,16 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-1.418867</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-1.34516</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.972541</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.60778</v>
       </c>
       <c r="H124" s="1" t="inlineStr">
         <is>
@@ -4365,16 +4365,16 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-1.418867</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-1.34516</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.972541</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.60778</v>
       </c>
       <c r="H125" s="1" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -8738,7 +8738,11 @@
           <t>Capital lease repayment</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -11617,7 +11621,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -11713,7 +11717,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13052,7 +13056,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">

--- a/output/pdf_financials_xlsx/PVT.xlsx
+++ b/output/pdf_financials_xlsx/PVT.xlsx
@@ -1660,16 +1660,16 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1.536415</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.8406130000000001</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.198363</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1.432396</v>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
@@ -1692,16 +1692,16 @@
         <v>7.350206</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>16.183727</v>
+        <v>17.720142</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17.75974</v>
+        <v>18.600353</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>11.600117</v>
+        <v>12.79848</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>13.236879</v>
+        <v>14.669275</v>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
@@ -1916,16 +1916,16 @@
         <v>2.122204</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.586374</v>
+        <v>1.049959</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.693769</v>
+        <v>1.853156</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.900014</v>
+        <v>3.701651</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.351327</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -2435,19 +2435,19 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>4.21124</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>2.252417</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>4.694552</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.673087</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>2.025381</v>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
@@ -2531,19 +2531,19 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.967836</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>4.076896</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>2.256046</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.615737</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.548116</v>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
@@ -3661,16 +3661,16 @@
         <v>0.392206</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>-0.40451</v>
+        <v>-0.300587</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.060817</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.244438</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.87247</v>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
@@ -3757,16 +3757,16 @@
         <v>1.095052</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-2.874503</v>
+        <v>-2.77058</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>1.039807</v>
+        <v>0.97899</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-3.519791</v>
+        <v>-3.275353</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.414309</v>
+        <v>0.458161</v>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
@@ -4240,13 +4240,13 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.229514</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-1.602534</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.23589</v>
       </c>
       <c r="H121" s="1" t="inlineStr">
         <is>
@@ -8268,7 +8268,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -8787,7 +8791,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
